--- a/data/trans_dic/P64D$bicicleta_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,44</t>
+          <t>0,18; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,02</t>
+          <t>0,14; 2,1</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,46</t>
+          <t>0,1; 2,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,02</t>
+          <t>0,08; 1,28</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,86</t>
+          <t>0,66; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,04</t>
+          <t>0,14; 4,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,92</t>
+          <t>0,84; 3,91</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,25</t>
+          <t>0,38; 4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,23</t>
+          <t>0,0; 70,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 53,28</t>
+          <t>0,58; 51,49</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,64</t>
+          <t>0,58; 4,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,31</t>
+          <t>0,1; 1,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,61</t>
+          <t>0,46; 2,45</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,11</t>
+          <t>0,23; 2,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,64</t>
+          <t>0,82; 3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,71</t>
+          <t>0,46; 2,66</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,9</t>
+          <t>0,77; 1,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 20,62</t>
+          <t>0,54; 20,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,62</t>
+          <t>0,92; 11,01</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>332; 6604</t>
+          <t>343; 6288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177; 6789</t>
+          <t>486; 7082</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 848</t>
+          <t>0; 903</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160; 4082</t>
+          <t>162; 4241</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>324; 4194</t>
+          <t>323; 5269</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1011; 8706</t>
+          <t>981; 8492</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>326; 4878</t>
+          <t>165; 4998</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2013; 10570</t>
+          <t>2271; 10531</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>496; 7116</t>
+          <t>639; 7917</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 176576</t>
+          <t>0; 181285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2474; 227058</t>
+          <t>2454; 219456</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3498</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 900</t>
+          <t>0; 763</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3731</t>
+          <t>0; 3494</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6603</t>
+          <t>0; 5786</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1274</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6088</t>
+          <t>0; 5904</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1535; 15519</t>
+          <t>1955; 15675</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>320; 4013</t>
+          <t>320; 3983</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2730; 16705</t>
+          <t>2929; 15709</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1425; 19513</t>
+          <t>1449; 18663</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1855; 9868</t>
+          <t>2222; 9909</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5348; 24349</t>
+          <t>4105; 23931</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14805; 37416</t>
+          <t>15077; 38597</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8516; 301237</t>
+          <t>7930; 299486</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31321; 398185</t>
+          <t>31386; 377216</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$bicicleta_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Provincia-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,27</t>
+          <t>0,47; 7,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,1</t>
+          <t>0,49; 4,11</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,56</t>
+          <t>0,41; 4,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,28</t>
+          <t>0,25; 2,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,71</t>
+          <t>0,62; 6,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,13</t>
+          <t>0,55; 4,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,91</t>
+          <t>0,94; 4,16</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,73</t>
+          <t>1,55; 15,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,05</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 51,49</t>
+          <t>1,31; 7,51</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,69</t>
+          <t>0,6; 5,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,3</t>
+          <t>0,19; 1,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,45</t>
+          <t>0,58; 2,85</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,97</t>
+          <t>0,76; 4,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,66</t>
+          <t>1,01; 4,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,66</t>
+          <t>1,22; 3,53</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,96</t>
+          <t>1,25; 2,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,5</t>
+          <t>0,69; 1,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 11,01</t>
+          <t>1,19; 2,23</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>4947</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>343; 6288</t>
+          <t>948; 14171</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>486; 7082</t>
+          <t>1727; 14526</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>4213</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 903</t>
+          <t>0; 7240</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>162; 4241</t>
+          <t>710; 8209</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>323; 5269</t>
+          <t>1087; 11182</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5517</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>981; 8492</t>
+          <t>924; 8983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>165; 4998</t>
+          <t>675; 5682</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2271; 10531</t>
+          <t>2555; 11344</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72934</t>
+          <t>12090</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>639; 7917</t>
+          <t>3247; 31812</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 181285</t>
+          <t>0; 6160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2454; 219456</t>
+          <t>5133; 29379</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>749</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>440</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>1189</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3948</t>
+          <t>0; 3768</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 763</t>
+          <t>0; 2292</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3494</t>
+          <t>0; 4613</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1717</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5786</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5904</t>
+          <t>0; 6493</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>9754</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1955; 15675</t>
+          <t>2306; 19461</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>320; 3983</t>
+          <t>704; 6733</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2929; 15709</t>
+          <t>4324; 21335</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>15819</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1449; 18663</t>
+          <t>3453; 19768</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2222; 9909</t>
+          <t>3160; 12950</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4105; 23931</t>
+          <t>9358; 27090</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15077; 38597</t>
+          <t>24122; 56489</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7930; 299486</t>
+          <t>10425; 24974</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31386; 377216</t>
+          <t>40842; 76760</t>
         </is>
       </c>
     </row>
